--- a/obspy/io/sitexml/tests/data/sera_site_no_sd.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_sd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC1E101-6951-284C-9E43-66065537A2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792E408D-9AEA-FA4B-89FE-02DB3DCF1D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="siteOwner" sheetId="4" r:id="rId1"/>
@@ -161,9 +161,6 @@
     <t>resonanceFrequency_description</t>
   </si>
   <si>
-    <t>resonanceFrequency_url</t>
-  </si>
-  <si>
     <t>velocityS30_value</t>
   </si>
   <si>
@@ -209,9 +206,6 @@
     <t>velocityS30_description</t>
   </si>
   <si>
-    <t>velocityS30_url</t>
-  </si>
-  <si>
     <t>velocityProfileCount</t>
   </si>
   <si>
@@ -251,9 +245,6 @@
     <t>velocityProfile_description</t>
   </si>
   <si>
-    <t>velocityProfile_url</t>
-  </si>
-  <si>
     <t>0.7</t>
   </si>
   <si>
@@ -381,6 +372,15 @@
   </si>
   <si>
     <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_uri</t>
+  </si>
+  <si>
+    <t>velocityS30_uri</t>
+  </si>
+  <si>
+    <t>velocityProfile_uri</t>
   </si>
 </sst>
 </file>
@@ -1851,61 +1851,61 @@
     </row>
     <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="21" t="s">
+      <c r="I2" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="K2" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G2" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2" s="9" t="s">
+      <c r="M2" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="O2" s="21" t="s">
         <v>105</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="M2" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>108</v>
       </c>
       <c r="P2" s="24">
         <v>12345</v>
       </c>
       <c r="Q2" s="21" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="R2" s="21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="S2" s="21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="T2" s="21" t="s">
         <v>20</v>
@@ -1988,121 +1988,121 @@
         <v>42</v>
       </c>
       <c r="Q1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AS1" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AT1" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="AU1" s="2" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:47" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5">
         <v>0.8</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -2123,13 +2123,13 @@
         <v>0.5</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="X2" s="4">
         <v>1</v>
@@ -2138,7 +2138,7 @@
         <v>23</v>
       </c>
       <c r="Z2" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AA2" s="5"/>
       <c r="AB2" s="9">
@@ -2148,7 +2148,7 @@
         <v>24</v>
       </c>
       <c r="AD2" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AE2" s="3" t="s">
         <v>25</v>
@@ -2178,7 +2178,7 @@
         <v>23</v>
       </c>
       <c r="AN2" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AO2" s="5"/>
       <c r="AP2" s="3">
@@ -2188,7 +2188,7 @@
         <v>24</v>
       </c>
       <c r="AR2" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AS2" s="3" t="s">
         <v>25</v>
@@ -2202,26 +2202,26 @@
     </row>
     <row r="3" spans="1:47" ht="128" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7">
         <v>1</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
@@ -2242,13 +2242,13 @@
         <v>0.7</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="X3" s="8">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>23</v>
       </c>
       <c r="Z3" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AA3" s="7"/>
       <c r="AB3" s="9">
@@ -2267,7 +2267,7 @@
         <v>24</v>
       </c>
       <c r="AD3" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AE3" s="6" t="s">
         <v>25</v>
@@ -2297,7 +2297,7 @@
         <v>23</v>
       </c>
       <c r="AN3" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AO3" s="7"/>
       <c r="AP3" s="6">
@@ -2307,7 +2307,7 @@
         <v>24</v>
       </c>
       <c r="AR3" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AS3" s="6" t="s">
         <v>25</v>
@@ -2321,26 +2321,26 @@
     </row>
     <row r="4" spans="1:47" ht="128" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7">
         <v>0.5</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -2361,13 +2361,13 @@
         <v>0.8</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="X4" s="8">
         <v>1</v>
@@ -2376,7 +2376,7 @@
         <v>23</v>
       </c>
       <c r="Z4" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AA4" s="7"/>
       <c r="AB4" s="9">
@@ -2386,7 +2386,7 @@
         <v>24</v>
       </c>
       <c r="AD4" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>25</v>
@@ -2395,7 +2395,7 @@
         <v>26</v>
       </c>
       <c r="AG4" s="15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AH4" s="8">
         <v>33</v>
@@ -2416,7 +2416,7 @@
         <v>23</v>
       </c>
       <c r="AN4" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AO4" s="7"/>
       <c r="AP4" s="6">
@@ -2426,7 +2426,7 @@
         <v>24</v>
       </c>
       <c r="AR4" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AS4" s="6" t="s">
         <v>25</v>
@@ -2440,47 +2440,47 @@
     </row>
     <row r="5" spans="1:47" ht="44" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D5" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7">
         <v>0.6</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K5" s="12"/>
       <c r="L5" s="9">
         <v>2023</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O5" s="16" t="s">
         <v>28</v>
       </c>
       <c r="P5" s="12"/>
       <c r="Q5" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="R5" s="8">
         <v>497</v>
@@ -2490,35 +2490,35 @@
         <v>0.8</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Y5" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Z5" s="13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AA5" s="12"/>
       <c r="AB5" s="9">
         <v>2023</v>
       </c>
       <c r="AC5" s="17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AD5" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AE5" s="16" t="s">
         <v>28</v>
       </c>
       <c r="AF5" s="12"/>
       <c r="AG5" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AH5" s="7"/>
       <c r="AI5" s="7"/>

--- a/obspy/io/sitexml/tests/data/sera_site_no_sd.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_sd.xlsx
@@ -1,422 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792E408D-9AEA-FA4B-89FE-02DB3DCF1D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="siteOwner" sheetId="4" r:id="rId1"/>
-    <sheet name="analysis" sheetId="3" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteOwner" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="117">
-  <si>
-    <t>ownerID</t>
-  </si>
-  <si>
-    <t>owner_codename</t>
-  </si>
-  <si>
-    <t>owner_fullname</t>
-  </si>
-  <si>
-    <t>personID</t>
-  </si>
-  <si>
-    <t>person_firstname</t>
-  </si>
-  <si>
-    <t>person_lastname</t>
-  </si>
-  <si>
-    <t>person_mbox</t>
-  </si>
-  <si>
-    <t>person_homepage</t>
-  </si>
-  <si>
-    <t>institutionID</t>
-  </si>
-  <si>
-    <t>institution_name</t>
-  </si>
-  <si>
-    <t>institution_mbox</t>
-  </si>
-  <si>
-    <t>institution_phone</t>
-  </si>
-  <si>
-    <t>institution_homepage</t>
-  </si>
-  <si>
-    <t>address_street</t>
-  </si>
-  <si>
-    <t>address_locality</t>
-  </si>
-  <si>
-    <t>address_postal_code</t>
-  </si>
-  <si>
-    <t>address_country_code</t>
-  </si>
-  <si>
-    <t>address_country</t>
-  </si>
-  <si>
-    <t>affiliation_department</t>
-  </si>
-  <si>
-    <t>affiliation_function</t>
-  </si>
-  <si>
-    <t>Senior researcher</t>
-  </si>
-  <si>
-    <t>siteID</t>
-  </si>
-  <si>
-    <t>siteDescriptionID</t>
-  </si>
-  <si>
-    <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-  </si>
-  <si>
-    <t>Bulletin Earthquake Engineering</t>
-  </si>
-  <si>
-    <t>10.1007/s10518-017-0135-5</t>
-  </si>
-  <si>
-    <t>paper</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-    </r>
-  </si>
-  <si>
-    <t>10.1002/nsg.12248</t>
-  </si>
-  <si>
-    <t>analysisID</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_value</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_uncertainty</t>
-  </si>
-  <si>
-    <t>resonanceFrequencyQindex1</t>
-  </si>
-  <si>
-    <t>resonanceFrequencyMethod1</t>
-  </si>
-  <si>
-    <t>resonanceFrequencyMethod2</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_title</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_firstAuthor</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_year</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_booktitle</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_language</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_doi</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_description</t>
-  </si>
-  <si>
-    <t>velocityS30_value</t>
-  </si>
-  <si>
-    <t>velocityS30_uncertainty</t>
-  </si>
-  <si>
-    <t>velocityS30Qindex1</t>
-  </si>
-  <si>
-    <t>velocityS30Method1</t>
-  </si>
-  <si>
-    <t>velocityS30Method2</t>
-  </si>
-  <si>
-    <t>velocityS30MethodCombIndex</t>
-  </si>
-  <si>
-    <t>velocityS30ManualIndex</t>
-  </si>
-  <si>
-    <t>velocityS30_title</t>
-  </si>
-  <si>
-    <t>velocityS30_firstAuthor</t>
-  </si>
-  <si>
-    <t>velocityS30_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>velocityS30_year</t>
-  </si>
-  <si>
-    <t>velocityS30_booktitle</t>
-  </si>
-  <si>
-    <t>velocityS30_language</t>
-  </si>
-  <si>
-    <t>velocityS30_doi</t>
-  </si>
-  <si>
-    <t>velocityS30_description</t>
-  </si>
-  <si>
-    <t>velocityProfileCount</t>
-  </si>
-  <si>
-    <t>sptLogsCount</t>
-  </si>
-  <si>
-    <t>cptLogsCount</t>
-  </si>
-  <si>
-    <t>boreholeLogsCount</t>
-  </si>
-  <si>
-    <t>velocityProfileQindex1</t>
-  </si>
-  <si>
-    <t>velocityProfile_title</t>
-  </si>
-  <si>
-    <t>velocityProfile_firstAuthor</t>
-  </si>
-  <si>
-    <t>velocityProfile_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>velocityProfile_year</t>
-  </si>
-  <si>
-    <t>velocityProfile_booktitle</t>
-  </si>
-  <si>
-    <t>velocityProfile_language</t>
-  </si>
-  <si>
-    <t>velocityProfile_doi</t>
-  </si>
-  <si>
-    <t>velocityProfile_description</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>HVSR NOISE</t>
-  </si>
-  <si>
-    <t>SSR NOISE</t>
-  </si>
-  <si>
-    <t>MASW</t>
-  </si>
-  <si>
-    <t>SPAC/F-K</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>S-REFL</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/nsg.12248</t>
-  </si>
-  <si>
-    <t>Near Surface Geophysics</t>
-  </si>
-  <si>
-    <t>http://www.domain.ab</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site_description/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site/002</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site_description/002</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/002</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/003</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/004</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/siteOwner/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/person/001</t>
-  </si>
-  <si>
-    <t>info@domain.ab</t>
-  </si>
-  <si>
-    <t>https://www.domain.ab/person</t>
-  </si>
-  <si>
-    <t>someemail@domain.ab</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Surname</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/institution/001</t>
-  </si>
-  <si>
-    <t>INSTITUTION_ABBR</t>
-  </si>
-  <si>
-    <t>+30 123 456789</t>
-  </si>
-  <si>
-    <t>Some streetAddress</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>Somecountry</t>
-  </si>
-  <si>
-    <t>Seismology</t>
-  </si>
-  <si>
-    <t>SITEOWNER</t>
-  </si>
-  <si>
-    <t>Site Owner Full Name</t>
-  </si>
-  <si>
-    <t>Author A.</t>
-  </si>
-  <si>
-    <t>Author B.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_uri</t>
-  </si>
-  <si>
-    <t>velocityS30_uri</t>
-  </si>
-  <si>
-    <t>velocityProfile_uri</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <b val="1"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -513,99 +143,99 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{600E5E3E-3C3F-3D42-957F-EDF86D356745}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -674,14 +304,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1756,790 +1378,1135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7AE111-1EFA-E748-84E0-0CB676D8C6E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="19" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" style="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" style="19" customWidth="1"/>
-    <col min="7" max="7" width="34.1640625" style="19" customWidth="1"/>
-    <col min="8" max="8" width="54.83203125" style="19" customWidth="1"/>
-    <col min="9" max="9" width="29" style="19" customWidth="1"/>
-    <col min="10" max="10" width="17" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="19" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" style="19" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" style="19" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" style="19" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" style="19" customWidth="1"/>
-    <col min="16" max="16" width="18.33203125" style="19" customWidth="1"/>
-    <col min="17" max="17" width="19.5" style="19" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" style="19" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" style="19" customWidth="1"/>
-    <col min="20" max="20" width="16.1640625" style="19" customWidth="1"/>
-    <col min="21" max="21" width="8.33203125" style="19" customWidth="1"/>
-    <col min="22" max="16384" width="8.33203125" style="19"/>
+    <col width="30.33203125" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
+    <col width="15.6640625" customWidth="1" style="19" min="2" max="2"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="19" min="3" max="3"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="19" min="4" max="4"/>
+    <col width="15.33203125" customWidth="1" style="19" min="5" max="5"/>
+    <col width="15.1640625" customWidth="1" style="19" min="6" max="6"/>
+    <col width="34.1640625" customWidth="1" style="19" min="7" max="7"/>
+    <col width="54.83203125" customWidth="1" style="19" min="8" max="8"/>
+    <col width="29" customWidth="1" style="19" min="9" max="9"/>
+    <col width="17" bestFit="1" customWidth="1" style="19" min="10" max="10"/>
+    <col width="14.6640625" customWidth="1" style="19" min="11" max="11"/>
+    <col width="15.1640625" customWidth="1" style="19" min="12" max="12"/>
+    <col width="18.6640625" customWidth="1" style="19" min="13" max="13"/>
+    <col width="28.6640625" customWidth="1" style="19" min="14" max="14"/>
+    <col width="14.33203125" customWidth="1" style="19" min="15" max="15"/>
+    <col width="18.33203125" customWidth="1" style="19" min="16" max="16"/>
+    <col width="19.5" customWidth="1" style="19" min="17" max="17"/>
+    <col width="14.6640625" customWidth="1" style="19" min="18" max="18"/>
+    <col width="18.83203125" customWidth="1" style="19" min="19" max="19"/>
+    <col width="16.1640625" customWidth="1" style="19" min="20" max="20"/>
+    <col width="8.33203125" customWidth="1" style="19" min="21" max="21"/>
+    <col width="8.33203125" customWidth="1" style="19" min="22" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="18" t="s">
-        <v>19</v>
+    <row r="1" ht="20.25" customHeight="1" s="26">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>ownerID</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>owner_codename</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>owner_fullname</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>personID</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>person_firstname</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>person_lastname</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>person_mbox</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>person_homepage</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>institutionID</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>institution_name</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>institution_mbox</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
+          <t>institution_phone</t>
+        </is>
+      </c>
+      <c r="M1" s="18" t="inlineStr">
+        <is>
+          <t>institution_homepage</t>
+        </is>
+      </c>
+      <c r="N1" s="18" t="inlineStr">
+        <is>
+          <t>address_street</t>
+        </is>
+      </c>
+      <c r="O1" s="18" t="inlineStr">
+        <is>
+          <t>address_locality</t>
+        </is>
+      </c>
+      <c r="P1" s="18" t="inlineStr">
+        <is>
+          <t>address_postal_code</t>
+        </is>
+      </c>
+      <c r="Q1" s="18" t="inlineStr">
+        <is>
+          <t>address_country_code</t>
+        </is>
+      </c>
+      <c r="R1" s="18" t="inlineStr">
+        <is>
+          <t>address_country</t>
+        </is>
+      </c>
+      <c r="S1" s="18" t="inlineStr">
+        <is>
+          <t>affiliation_department</t>
+        </is>
+      </c>
+      <c r="T1" s="18" t="inlineStr">
+        <is>
+          <t>affiliation_function</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="M2" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="P2" s="24">
+    <row r="2" ht="20.25" customHeight="1" s="26">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/siteOwner/001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>SITEOWNER</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Site Owner Full Name</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/person/001</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>Surname</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>someemail@domain.ab</t>
+        </is>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>https://www.domain.ab/person</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/institution/001</t>
+        </is>
+      </c>
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t>INSTITUTION_ABBR</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>info@domain.ab</t>
+        </is>
+      </c>
+      <c r="L2" s="23" t="inlineStr">
+        <is>
+          <t>+30 123 456789</t>
+        </is>
+      </c>
+      <c r="M2" s="21" t="inlineStr">
+        <is>
+          <t>http://www.domain.ab</t>
+        </is>
+      </c>
+      <c r="N2" s="21" t="inlineStr">
+        <is>
+          <t>Some streetAddress</t>
+        </is>
+      </c>
+      <c r="O2" s="21" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="P2" s="24" t="n">
         <v>12345</v>
       </c>
-      <c r="Q2" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="R2" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="S2" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="T2" s="21" t="s">
-        <v>20</v>
+      <c r="Q2" s="21" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="R2" s="21" t="inlineStr">
+        <is>
+          <t>Somecountry</t>
+        </is>
+      </c>
+      <c r="S2" s="21" t="inlineStr">
+        <is>
+          <t>Seismology</t>
+        </is>
+      </c>
+      <c r="T2" s="21" t="inlineStr">
+        <is>
+          <t>Senior researcher</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="isterre.fr/person/001" xr:uid="{B524591F-5FF0-224F-AE21-10B1AFE4E766}"/>
-    <hyperlink ref="M2" r:id="rId2" display="http://www.isterre.fr" xr:uid="{A4CF2504-4AF0-074F-AEE2-E6DBA31220CC}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" display="isterre.fr/person/001" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" display="http://www.isterre.fr" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:AT5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="16.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20" style="1" customWidth="1"/>
-    <col min="4" max="48" width="16.33203125" style="1" customWidth="1"/>
-    <col min="49" max="16384" width="16.33203125" style="1"/>
+    <col width="16.33203125" customWidth="1" style="1" min="1" max="2"/>
+    <col width="20" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16.33203125" customWidth="1" style="1" min="4" max="48"/>
+    <col width="16.33203125" customWidth="1" style="1" min="49" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AQ1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AS1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU1" s="2" t="s">
-        <v>116</v>
+    <row r="1" ht="44.25" customHeight="1" s="26">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>siteID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>siteDescriptionID</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>analysisID</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_value</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_uncertainty</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequencyQindex1</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequencyMethod1</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequencyMethod2</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_title</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_firstAuthor</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_year</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_booktitle</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_language</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_doi</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_description</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_uri</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_value</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_uncertainty</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30Qindex1</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30Method1</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30Method2</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30MethodCombIndex</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30ManualIndex</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_title</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_firstAuthor</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_year</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_booktitle</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_language</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_doi</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_description</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>velocityS30_uri</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>sptLogsCount</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>cptLogsCount</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>boreholeLogsCount</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfileQindex1</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_title</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_firstAuthor</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_year</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_booktitle</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_language</t>
+        </is>
+      </c>
+      <c r="AR1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_doi</t>
+        </is>
+      </c>
+      <c r="AS1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_description</t>
+        </is>
+      </c>
+      <c r="AT1" s="2" t="inlineStr">
+        <is>
+          <t>velocityProfile_uri</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5">
+    <row r="2" ht="128.25" customHeight="1" s="26">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/001</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/001</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/001</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="4">
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>HVSR NOISE</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>SSR NOISE</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n">
         <v>620</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="X2" s="4">
+      <c r="U2" s="9" t="inlineStr">
+        <is>
+          <t>MASW</t>
+        </is>
+      </c>
+      <c r="V2" s="9" t="inlineStr">
+        <is>
+          <t>SPAC/F-K</t>
+        </is>
+      </c>
+      <c r="W2" s="9" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="X2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Y2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z2" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="9">
+      <c r="Y2" s="9" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="Z2" s="14" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="9" t="n">
         <v>2018</v>
       </c>
-      <c r="AC2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD2" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH2" s="4">
-        <v>33</v>
-      </c>
-      <c r="AI2" s="4">
+      <c r="AC2" s="9" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AD2" s="14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AE2" s="9" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AF2" s="9" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AG2" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="AH2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" s="4">
+      <c r="AI2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" s="4">
+      <c r="AJ2" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AL2" s="4">
+      <c r="AK2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AM2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AN2" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="3">
+      <c r="AL2" s="9" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="AM2" s="14" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AN2" s="10" t="n"/>
+      <c r="AO2" s="9" t="n">
         <v>2018</v>
       </c>
-      <c r="AQ2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AR2" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="AS2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AT2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AU2" s="3" t="s">
-        <v>27</v>
+      <c r="AP2" s="9" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AQ2" s="14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AR2" s="9" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AS2" s="9" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AT2" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="128" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7">
+    <row r="3" ht="128" customHeight="1" s="26">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/001</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/001</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/002</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="8">
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>HVSR NOISE</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>SSR NOISE</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="12" t="n"/>
+      <c r="L3" s="11" t="n"/>
+      <c r="M3" s="12" t="n"/>
+      <c r="N3" s="12" t="n"/>
+      <c r="O3" s="12" t="n"/>
+      <c r="P3" s="12" t="n"/>
+      <c r="Q3" s="12" t="n"/>
+      <c r="R3" s="12" t="n">
         <v>620</v>
       </c>
-      <c r="S3" s="8">
+      <c r="S3" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="T3" s="7">
+      <c r="T3" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="U3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="X3" s="8">
+      <c r="U3" s="9" t="inlineStr">
+        <is>
+          <t>MASW</t>
+        </is>
+      </c>
+      <c r="V3" s="11" t="inlineStr">
+        <is>
+          <t>SPAC/F-K</t>
+        </is>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="X3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z3" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="9">
+      <c r="Y3" s="11" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="Z3" s="14" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="n"/>
+      <c r="AB3" s="9" t="n">
         <v>2018</v>
       </c>
-      <c r="AC3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH3" s="8">
-        <v>33</v>
-      </c>
-      <c r="AI3" s="8">
+      <c r="AC3" s="11" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AD3" s="16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AE3" s="11" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AF3" s="11" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AG3" s="11" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="AH3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" s="8">
+      <c r="AI3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AK3" s="8">
+      <c r="AJ3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AL3" s="8">
+      <c r="AK3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="AM3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AN3" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="AO3" s="7"/>
-      <c r="AP3" s="6">
+      <c r="AL3" s="11" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="AM3" s="14" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AN3" s="12" t="n"/>
+      <c r="AO3" s="11" t="n">
         <v>2018</v>
       </c>
-      <c r="AQ3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="AR3" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="AS3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AT3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AU3" s="6" t="s">
-        <v>27</v>
+      <c r="AP3" s="11" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AQ3" s="16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AR3" s="11" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AS3" s="11" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AT3" s="11" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="128" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7">
+    <row r="4" ht="128" customHeight="1" s="26">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/001</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/001</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/003</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="8">
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>HVSR NOISE</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>SSR NOISE</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="12" t="n"/>
+      <c r="N4" s="12" t="n"/>
+      <c r="O4" s="12" t="n"/>
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="12" t="n">
         <v>620</v>
       </c>
-      <c r="S4" s="8">
+      <c r="S4" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="T4" s="7">
+      <c r="T4" s="12" t="n">
         <v>0.8</v>
       </c>
-      <c r="U4" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="X4" s="8">
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>MASW</t>
+        </is>
+      </c>
+      <c r="V4" s="11" t="inlineStr">
+        <is>
+          <t>SPAC/F-K</t>
+        </is>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="X4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z4" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="9">
+      <c r="Y4" s="11" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="Z4" s="14" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AA4" s="12" t="n"/>
+      <c r="AB4" s="9" t="n">
         <v>2018</v>
       </c>
-      <c r="AC4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD4" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG4" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="AH4" s="8">
-        <v>33</v>
-      </c>
-      <c r="AI4" s="8">
+      <c r="AC4" s="11" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AD4" s="16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AE4" s="11" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AF4" s="11" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AG4" s="16" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="AH4" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" s="8">
+      <c r="AI4" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AK4" s="8">
+      <c r="AJ4" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AL4" s="8">
+      <c r="AK4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="AM4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AN4" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="AO4" s="7"/>
-      <c r="AP4" s="6">
+      <c r="AL4" s="11" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="AM4" s="14" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AN4" s="12" t="n"/>
+      <c r="AO4" s="11" t="n">
         <v>2018</v>
       </c>
-      <c r="AQ4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="AR4" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="AS4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="AT4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AU4" s="6" t="s">
-        <v>27</v>
+      <c r="AP4" s="11" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AQ4" s="16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AR4" s="11" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AS4" s="11" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AT4" s="11" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="44" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7">
+    <row r="5" ht="44" customHeight="1" s="26">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/002</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/002</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/004</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="9">
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>SSR NOISE</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="9" t="n">
         <v>2023</v>
       </c>
-      <c r="M5" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" s="8">
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="n"/>
+      <c r="Q5" s="11" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="n">
         <v>497</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7">
+      <c r="S5" s="12" t="n"/>
+      <c r="T5" s="12" t="n">
         <v>0.8</v>
       </c>
-      <c r="U5" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y5" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z5" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="9">
+      <c r="U5" s="11" t="inlineStr">
+        <is>
+          <t>S-REFL</t>
+        </is>
+      </c>
+      <c r="V5" s="12" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="11" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="Y5" s="9" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="Z5" s="14" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="n"/>
+      <c r="AB5" s="9" t="n">
         <v>2023</v>
       </c>
-      <c r="AC5" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD5" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE5" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH5" s="7"/>
-      <c r="AI5" s="7"/>
-      <c r="AJ5" s="7"/>
-      <c r="AK5" s="7"/>
-      <c r="AL5" s="7"/>
-      <c r="AM5" s="7"/>
-      <c r="AN5" s="7"/>
-      <c r="AO5" s="7"/>
-      <c r="AP5" s="6"/>
-      <c r="AQ5" s="7"/>
-      <c r="AR5" s="7"/>
-      <c r="AS5" s="7"/>
-      <c r="AT5" s="7"/>
-      <c r="AU5" s="7"/>
+      <c r="AC5" s="17" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="AD5" s="17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AE5" s="16" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AF5" s="12" t="n"/>
+      <c r="AG5" s="11" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AH5" s="12" t="n"/>
+      <c r="AI5" s="12" t="n"/>
+      <c r="AJ5" s="12" t="n"/>
+      <c r="AK5" s="12" t="n"/>
+      <c r="AL5" s="12" t="n"/>
+      <c r="AM5" s="12" t="n"/>
+      <c r="AN5" s="12" t="n"/>
+      <c r="AO5" s="11" t="n"/>
+      <c r="AP5" s="12" t="n"/>
+      <c r="AQ5" s="12" t="n"/>
+      <c r="AR5" s="12" t="n"/>
+      <c r="AS5" s="12" t="n"/>
+      <c r="AT5" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/obspy/io/sitexml/tests/data/sera_site_no_sd.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_sd.xlsx
@@ -1,52 +1,400 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFC7B17-4B0F-0445-9045-323E8DFD6ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteOwner" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="siteOwner" sheetId="1" r:id="rId1"/>
+    <sheet name="analysis" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="115">
+  <si>
+    <t>ownerID</t>
+  </si>
+  <si>
+    <t>owner_codename</t>
+  </si>
+  <si>
+    <t>owner_fullname</t>
+  </si>
+  <si>
+    <t>personID</t>
+  </si>
+  <si>
+    <t>person_firstname</t>
+  </si>
+  <si>
+    <t>person_lastname</t>
+  </si>
+  <si>
+    <t>person_mbox</t>
+  </si>
+  <si>
+    <t>person_homepage</t>
+  </si>
+  <si>
+    <t>institutionID</t>
+  </si>
+  <si>
+    <t>institution_name</t>
+  </si>
+  <si>
+    <t>institution_mbox</t>
+  </si>
+  <si>
+    <t>institution_phone</t>
+  </si>
+  <si>
+    <t>institution_homepage</t>
+  </si>
+  <si>
+    <t>address_street</t>
+  </si>
+  <si>
+    <t>address_locality</t>
+  </si>
+  <si>
+    <t>address_postal_code</t>
+  </si>
+  <si>
+    <t>address_country_code</t>
+  </si>
+  <si>
+    <t>address_country</t>
+  </si>
+  <si>
+    <t>affiliation_department</t>
+  </si>
+  <si>
+    <t>affiliation_function</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/siteOwner/001</t>
+  </si>
+  <si>
+    <t>SITEOWNER</t>
+  </si>
+  <si>
+    <t>Site Owner Full Name</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/person/001</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Surname</t>
+  </si>
+  <si>
+    <t>someemail@domain.ab</t>
+  </si>
+  <si>
+    <t>https://www.domain.ab/person</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/institution/001</t>
+  </si>
+  <si>
+    <t>INSTITUTION_ABBR</t>
+  </si>
+  <si>
+    <t>info@domain.ab</t>
+  </si>
+  <si>
+    <t>+30 123 456789</t>
+  </si>
+  <si>
+    <t>http://www.domain.ab</t>
+  </si>
+  <si>
+    <t>Some streetAddress</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>Somecountry</t>
+  </si>
+  <si>
+    <t>Seismology</t>
+  </si>
+  <si>
+    <t>Senior researcher</t>
+  </si>
+  <si>
+    <t>siteID</t>
+  </si>
+  <si>
+    <t>siteDescriptionID</t>
+  </si>
+  <si>
+    <t>analysisID</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_value</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_uncertainty</t>
+  </si>
+  <si>
+    <t>resonanceFrequencyQindex1</t>
+  </si>
+  <si>
+    <t>resonanceFrequencyMethod1</t>
+  </si>
+  <si>
+    <t>resonanceFrequencyMethod2</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_title</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_firstAuthor</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_secondaryAuthors</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_year</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_booktitle</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_language</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_doi</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_description</t>
+  </si>
+  <si>
+    <t>resonanceFrequency_uri</t>
+  </si>
+  <si>
+    <t>velocityS30_value</t>
+  </si>
+  <si>
+    <t>velocityS30_uncertainty</t>
+  </si>
+  <si>
+    <t>velocityS30Qindex1</t>
+  </si>
+  <si>
+    <t>velocityS30Method1</t>
+  </si>
+  <si>
+    <t>velocityS30Method2</t>
+  </si>
+  <si>
+    <t>velocityS30MethodCombIndex</t>
+  </si>
+  <si>
+    <t>velocityS30ManualIndex</t>
+  </si>
+  <si>
+    <t>velocityS30_title</t>
+  </si>
+  <si>
+    <t>velocityS30_firstAuthor</t>
+  </si>
+  <si>
+    <t>velocityS30_secondaryAuthors</t>
+  </si>
+  <si>
+    <t>velocityS30_year</t>
+  </si>
+  <si>
+    <t>velocityS30_booktitle</t>
+  </si>
+  <si>
+    <t>velocityS30_language</t>
+  </si>
+  <si>
+    <t>velocityS30_doi</t>
+  </si>
+  <si>
+    <t>velocityS30_description</t>
+  </si>
+  <si>
+    <t>velocityS30_uri</t>
+  </si>
+  <si>
+    <t>sptLogsCount</t>
+  </si>
+  <si>
+    <t>cptLogsCount</t>
+  </si>
+  <si>
+    <t>boreholeLogsCount</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/site/001</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/site_description/001</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/analysis/001</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>HVSR NOISE</t>
+  </si>
+  <si>
+    <t>SSR NOISE</t>
+  </si>
+  <si>
+    <t>MASW</t>
+  </si>
+  <si>
+    <t>SPAC/F-K</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+  </si>
+  <si>
+    <t>Author A.</t>
+  </si>
+  <si>
+    <t>Bulletin Earthquake Engineering</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>10.1007/s10518-017-0135-5</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/analysis/002</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/analysis/003</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/site/002</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/site_description/002</t>
+  </si>
+  <si>
+    <t>quakeml:domain.ab/analysis/004</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+  </si>
+  <si>
+    <t>Author B.</t>
+  </si>
+  <si>
+    <t>Near Surface Geophysics</t>
+  </si>
+  <si>
+    <t>10.1002/nsg.12248</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/nsg.12248</t>
+  </si>
+  <si>
+    <t>S-REFL</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>velocityProfileSetQindex1</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_title</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_firstAuthor</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_secondaryAuthors</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_year</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_booktitle</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_language</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_doi</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_description</t>
+  </si>
+  <si>
+    <t>velocityProfileSet_uri</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
-      <b val="1"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
-      <color indexed="8"/>
-      <sz val="10"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-      <color indexed="8"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -143,98 +491,71 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -304,6 +625,14 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1378,1135 +1707,776 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="30.33203125" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
-    <col width="15.6640625" customWidth="1" style="19" min="2" max="2"/>
-    <col width="17.5" bestFit="1" customWidth="1" style="19" min="3" max="3"/>
-    <col width="25.5" bestFit="1" customWidth="1" style="19" min="4" max="4"/>
-    <col width="15.33203125" customWidth="1" style="19" min="5" max="5"/>
-    <col width="15.1640625" customWidth="1" style="19" min="6" max="6"/>
-    <col width="34.1640625" customWidth="1" style="19" min="7" max="7"/>
-    <col width="54.83203125" customWidth="1" style="19" min="8" max="8"/>
-    <col width="29" customWidth="1" style="19" min="9" max="9"/>
-    <col width="17" bestFit="1" customWidth="1" style="19" min="10" max="10"/>
-    <col width="14.6640625" customWidth="1" style="19" min="11" max="11"/>
-    <col width="15.1640625" customWidth="1" style="19" min="12" max="12"/>
-    <col width="18.6640625" customWidth="1" style="19" min="13" max="13"/>
-    <col width="28.6640625" customWidth="1" style="19" min="14" max="14"/>
-    <col width="14.33203125" customWidth="1" style="19" min="15" max="15"/>
-    <col width="18.33203125" customWidth="1" style="19" min="16" max="16"/>
-    <col width="19.5" customWidth="1" style="19" min="17" max="17"/>
-    <col width="14.6640625" customWidth="1" style="19" min="18" max="18"/>
-    <col width="18.83203125" customWidth="1" style="19" min="19" max="19"/>
-    <col width="16.1640625" customWidth="1" style="19" min="20" max="20"/>
-    <col width="8.33203125" customWidth="1" style="19" min="21" max="21"/>
-    <col width="8.33203125" customWidth="1" style="19" min="22" max="16384"/>
+    <col min="1" max="1" width="30.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="34.1640625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="54.83203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="29" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" style="10" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="28.6640625" style="10" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" style="10" customWidth="1"/>
+    <col min="17" max="17" width="19.5" style="10" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" style="10" customWidth="1"/>
+    <col min="19" max="19" width="18.83203125" style="10" customWidth="1"/>
+    <col min="20" max="20" width="16.1640625" style="10" customWidth="1"/>
+    <col min="21" max="22" width="8.33203125" style="10" customWidth="1"/>
+    <col min="23" max="16384" width="8.33203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" s="26">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>ownerID</t>
-        </is>
-      </c>
-      <c r="B1" s="18" t="inlineStr">
-        <is>
-          <t>owner_codename</t>
-        </is>
-      </c>
-      <c r="C1" s="18" t="inlineStr">
-        <is>
-          <t>owner_fullname</t>
-        </is>
-      </c>
-      <c r="D1" s="18" t="inlineStr">
-        <is>
-          <t>personID</t>
-        </is>
-      </c>
-      <c r="E1" s="18" t="inlineStr">
-        <is>
-          <t>person_firstname</t>
-        </is>
-      </c>
-      <c r="F1" s="18" t="inlineStr">
-        <is>
-          <t>person_lastname</t>
-        </is>
-      </c>
-      <c r="G1" s="18" t="inlineStr">
-        <is>
-          <t>person_mbox</t>
-        </is>
-      </c>
-      <c r="H1" s="18" t="inlineStr">
-        <is>
-          <t>person_homepage</t>
-        </is>
-      </c>
-      <c r="I1" s="18" t="inlineStr">
-        <is>
-          <t>institutionID</t>
-        </is>
-      </c>
-      <c r="J1" s="18" t="inlineStr">
-        <is>
-          <t>institution_name</t>
-        </is>
-      </c>
-      <c r="K1" s="18" t="inlineStr">
-        <is>
-          <t>institution_mbox</t>
-        </is>
-      </c>
-      <c r="L1" s="18" t="inlineStr">
-        <is>
-          <t>institution_phone</t>
-        </is>
-      </c>
-      <c r="M1" s="18" t="inlineStr">
-        <is>
-          <t>institution_homepage</t>
-        </is>
-      </c>
-      <c r="N1" s="18" t="inlineStr">
-        <is>
-          <t>address_street</t>
-        </is>
-      </c>
-      <c r="O1" s="18" t="inlineStr">
-        <is>
-          <t>address_locality</t>
-        </is>
-      </c>
-      <c r="P1" s="18" t="inlineStr">
-        <is>
-          <t>address_postal_code</t>
-        </is>
-      </c>
-      <c r="Q1" s="18" t="inlineStr">
-        <is>
-          <t>address_country_code</t>
-        </is>
-      </c>
-      <c r="R1" s="18" t="inlineStr">
-        <is>
-          <t>address_country</t>
-        </is>
-      </c>
-      <c r="S1" s="18" t="inlineStr">
-        <is>
-          <t>affiliation_department</t>
-        </is>
-      </c>
-      <c r="T1" s="18" t="inlineStr">
-        <is>
-          <t>affiliation_function</t>
-        </is>
+    <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1" s="26">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/siteOwner/001</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>SITEOWNER</t>
-        </is>
-      </c>
-      <c r="C2" s="21" t="inlineStr">
-        <is>
-          <t>Site Owner Full Name</t>
-        </is>
-      </c>
-      <c r="D2" s="21" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/person/001</t>
-        </is>
-      </c>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="F2" s="21" t="inlineStr">
-        <is>
-          <t>Surname</t>
-        </is>
-      </c>
-      <c r="G2" s="22" t="inlineStr">
-        <is>
-          <t>someemail@domain.ab</t>
-        </is>
-      </c>
-      <c r="H2" s="21" t="inlineStr">
-        <is>
-          <t>https://www.domain.ab/person</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/institution/001</t>
-        </is>
-      </c>
-      <c r="J2" s="21" t="inlineStr">
-        <is>
-          <t>INSTITUTION_ABBR</t>
-        </is>
-      </c>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>info@domain.ab</t>
-        </is>
-      </c>
-      <c r="L2" s="23" t="inlineStr">
-        <is>
-          <t>+30 123 456789</t>
-        </is>
-      </c>
-      <c r="M2" s="21" t="inlineStr">
-        <is>
-          <t>http://www.domain.ab</t>
-        </is>
-      </c>
-      <c r="N2" s="21" t="inlineStr">
-        <is>
-          <t>Some streetAddress</t>
-        </is>
-      </c>
-      <c r="O2" s="21" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="P2" s="24" t="n">
+    <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="15">
         <v>12345</v>
       </c>
-      <c r="Q2" s="21" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="R2" s="21" t="inlineStr">
-        <is>
-          <t>Somecountry</t>
-        </is>
-      </c>
-      <c r="S2" s="21" t="inlineStr">
-        <is>
-          <t>Seismology</t>
-        </is>
-      </c>
-      <c r="T2" s="21" t="inlineStr">
-        <is>
-          <t>Senior researcher</t>
-        </is>
+      <c r="Q2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" display="isterre.fr/person/001" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" display="http://www.isterre.fr" r:id="rId2"/>
+    <hyperlink ref="D2" r:id="rId1" display="isterre.fr/person/001" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M2" r:id="rId2" display="http://www.isterre.fr" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddHeader/>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AT5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="16.33203125" customWidth="1" style="1" min="1" max="2"/>
-    <col width="20" customWidth="1" style="1" min="3" max="3"/>
-    <col width="16.33203125" customWidth="1" style="1" min="4" max="48"/>
-    <col width="16.33203125" customWidth="1" style="1" min="49" max="16384"/>
+    <col min="1" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="49" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="44.25" customHeight="1" s="26">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>siteID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>siteDescriptionID</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>analysisID</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_value</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_uncertainty</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequencyQindex1</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequencyMethod1</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequencyMethod2</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_title</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_firstAuthor</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_secondaryAuthors</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_year</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_booktitle</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_language</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_doi</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_description</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>resonanceFrequency_uri</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_value</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_uncertainty</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30Qindex1</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30Method1</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30Method2</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30MethodCombIndex</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30ManualIndex</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_title</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_firstAuthor</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_secondaryAuthors</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_year</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_booktitle</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_language</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_doi</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_description</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>velocityS30_uri</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>sptLogsCount</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>cptLogsCount</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>boreholeLogsCount</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfileQindex1</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_title</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_firstAuthor</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_secondaryAuthors</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_year</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_booktitle</t>
-        </is>
-      </c>
-      <c r="AQ1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_language</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_doi</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_description</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>velocityProfile_uri</t>
-        </is>
+    <row r="1" spans="1:46" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="2" ht="128.25" customHeight="1" s="26">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site/001</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site_description/001</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/analysis/001</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n">
+    <row r="2" spans="1:46" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3">
         <v>0.8</v>
       </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>HVSR NOISE</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>SSR NOISE</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n">
+      <c r="G2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3">
         <v>620</v>
       </c>
-      <c r="S2" s="10" t="n">
+      <c r="S2" s="3">
         <v>18</v>
       </c>
-      <c r="T2" s="10" t="n">
+      <c r="T2" s="3">
         <v>0.5</v>
       </c>
-      <c r="U2" s="9" t="inlineStr">
-        <is>
-          <t>MASW</t>
-        </is>
-      </c>
-      <c r="V2" s="9" t="inlineStr">
-        <is>
-          <t>SPAC/F-K</t>
-        </is>
-      </c>
-      <c r="W2" s="9" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="X2" s="10" t="n">
+      <c r="U2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="X2" s="3">
         <v>1</v>
       </c>
-      <c r="Y2" s="9" t="inlineStr">
-        <is>
-          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-        </is>
-      </c>
-      <c r="Z2" s="14" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="9" t="n">
+      <c r="Y2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="2">
         <v>2018</v>
       </c>
-      <c r="AC2" s="9" t="inlineStr">
-        <is>
-          <t>Bulletin Earthquake Engineering</t>
-        </is>
-      </c>
-      <c r="AD2" s="14" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AE2" s="9" t="inlineStr">
-        <is>
-          <t>10.1007/s10518-017-0135-5</t>
-        </is>
-      </c>
-      <c r="AF2" s="9" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="AG2" s="9" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-        </is>
-      </c>
-      <c r="AH2" s="10" t="n">
+      <c r="AC2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH2" s="3">
         <v>0</v>
       </c>
-      <c r="AI2" s="10" t="n">
+      <c r="AI2" s="3">
         <v>0</v>
       </c>
-      <c r="AJ2" s="10" t="n">
+      <c r="AJ2" s="3">
         <v>0</v>
       </c>
-      <c r="AK2" s="10" t="n">
+      <c r="AK2" s="3">
         <v>1</v>
       </c>
-      <c r="AL2" s="9" t="inlineStr">
-        <is>
-          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-        </is>
-      </c>
-      <c r="AM2" s="14" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="AN2" s="10" t="n"/>
-      <c r="AO2" s="9" t="n">
+      <c r="AL2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="2">
         <v>2018</v>
       </c>
-      <c r="AP2" s="9" t="inlineStr">
-        <is>
-          <t>Bulletin Earthquake Engineering</t>
-        </is>
-      </c>
-      <c r="AQ2" s="14" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AR2" s="9" t="inlineStr">
-        <is>
-          <t>10.1007/s10518-017-0135-5</t>
-        </is>
-      </c>
-      <c r="AS2" s="9" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="AT2" s="9" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-        </is>
+      <c r="AP2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT2" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="3" ht="128" customHeight="1" s="26">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site/001</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site_description/001</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/analysis/002</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="12" t="n">
+    <row r="3" spans="1:46" ht="128" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>HVSR NOISE</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>SSR NOISE</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="n"/>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
-      <c r="Q3" s="12" t="n"/>
-      <c r="R3" s="12" t="n">
+      <c r="G3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5">
         <v>620</v>
       </c>
-      <c r="S3" s="12" t="n">
+      <c r="S3" s="5">
         <v>18</v>
       </c>
-      <c r="T3" s="12" t="n">
+      <c r="T3" s="5">
         <v>0.7</v>
       </c>
-      <c r="U3" s="9" t="inlineStr">
-        <is>
-          <t>MASW</t>
-        </is>
-      </c>
-      <c r="V3" s="11" t="inlineStr">
-        <is>
-          <t>SPAC/F-K</t>
-        </is>
-      </c>
-      <c r="W3" s="11" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="X3" s="12" t="n">
+      <c r="U3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="X3" s="5">
         <v>1</v>
       </c>
-      <c r="Y3" s="11" t="inlineStr">
-        <is>
-          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-        </is>
-      </c>
-      <c r="Z3" s="14" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="AA3" s="12" t="n"/>
-      <c r="AB3" s="9" t="n">
+      <c r="Y3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="2">
         <v>2018</v>
       </c>
-      <c r="AC3" s="11" t="inlineStr">
-        <is>
-          <t>Bulletin Earthquake Engineering</t>
-        </is>
-      </c>
-      <c r="AD3" s="16" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AE3" s="11" t="inlineStr">
-        <is>
-          <t>10.1007/s10518-017-0135-5</t>
-        </is>
-      </c>
-      <c r="AF3" s="11" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="AG3" s="11" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-        </is>
-      </c>
-      <c r="AH3" s="12" t="n">
+      <c r="AC3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH3" s="5">
         <v>0</v>
       </c>
-      <c r="AI3" s="12" t="n">
+      <c r="AI3" s="5">
         <v>0</v>
       </c>
-      <c r="AJ3" s="12" t="n">
+      <c r="AJ3" s="5">
         <v>0</v>
       </c>
-      <c r="AK3" s="12" t="n">
+      <c r="AK3" s="5">
         <v>1</v>
       </c>
-      <c r="AL3" s="11" t="inlineStr">
-        <is>
-          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-        </is>
-      </c>
-      <c r="AM3" s="14" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="AN3" s="12" t="n"/>
-      <c r="AO3" s="11" t="n">
+      <c r="AL3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM3" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="4">
         <v>2018</v>
       </c>
-      <c r="AP3" s="11" t="inlineStr">
-        <is>
-          <t>Bulletin Earthquake Engineering</t>
-        </is>
-      </c>
-      <c r="AQ3" s="16" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AR3" s="11" t="inlineStr">
-        <is>
-          <t>10.1007/s10518-017-0135-5</t>
-        </is>
-      </c>
-      <c r="AS3" s="11" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="AT3" s="11" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-        </is>
+      <c r="AP3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AS3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT3" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="4" ht="128" customHeight="1" s="26">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site/001</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site_description/001</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/analysis/003</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n">
+    <row r="4" spans="1:46" ht="128" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5">
         <v>0.5</v>
       </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>HVSR NOISE</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>SSR NOISE</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="n"/>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="L4" s="11" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="12" t="n"/>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="12" t="n">
+      <c r="G4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5">
         <v>620</v>
       </c>
-      <c r="S4" s="12" t="n">
+      <c r="S4" s="5">
         <v>18</v>
       </c>
-      <c r="T4" s="12" t="n">
+      <c r="T4" s="5">
         <v>0.8</v>
       </c>
-      <c r="U4" s="11" t="inlineStr">
-        <is>
-          <t>MASW</t>
-        </is>
-      </c>
-      <c r="V4" s="11" t="inlineStr">
-        <is>
-          <t>SPAC/F-K</t>
-        </is>
-      </c>
-      <c r="W4" s="11" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="X4" s="12" t="n">
+      <c r="U4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="X4" s="5">
         <v>1</v>
       </c>
-      <c r="Y4" s="11" t="inlineStr">
-        <is>
-          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-        </is>
-      </c>
-      <c r="Z4" s="14" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="AA4" s="12" t="n"/>
-      <c r="AB4" s="9" t="n">
+      <c r="Y4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="2">
         <v>2018</v>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
-        <is>
-          <t>Bulletin Earthquake Engineering</t>
-        </is>
-      </c>
-      <c r="AD4" s="16" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AE4" s="11" t="inlineStr">
-        <is>
-          <t>10.1007/s10518-017-0135-5</t>
-        </is>
-      </c>
-      <c r="AF4" s="11" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="AG4" s="16" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-        </is>
-      </c>
-      <c r="AH4" s="12" t="n">
+      <c r="AC4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH4" s="5">
         <v>0</v>
       </c>
-      <c r="AI4" s="12" t="n">
+      <c r="AI4" s="5">
         <v>0</v>
       </c>
-      <c r="AJ4" s="12" t="n">
+      <c r="AJ4" s="5">
         <v>0</v>
       </c>
-      <c r="AK4" s="12" t="n">
+      <c r="AK4" s="5">
         <v>1</v>
       </c>
-      <c r="AL4" s="11" t="inlineStr">
-        <is>
-          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-        </is>
-      </c>
-      <c r="AM4" s="14" t="inlineStr">
-        <is>
-          <t>Author A.</t>
-        </is>
-      </c>
-      <c r="AN4" s="12" t="n"/>
-      <c r="AO4" s="11" t="n">
+      <c r="AL4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN4" s="5"/>
+      <c r="AO4" s="4">
         <v>2018</v>
       </c>
-      <c r="AP4" s="11" t="inlineStr">
-        <is>
-          <t>Bulletin Earthquake Engineering</t>
-        </is>
-      </c>
-      <c r="AQ4" s="16" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AR4" s="11" t="inlineStr">
-        <is>
-          <t>10.1007/s10518-017-0135-5</t>
-        </is>
-      </c>
-      <c r="AS4" s="11" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="AT4" s="11" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-        </is>
+      <c r="AP4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AS4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT4" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1" s="26">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site/002</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/site_description/002</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>quakeml:domain.ab/analysis/004</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n">
+    <row r="5" spans="1:46" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5">
         <v>0.6</v>
       </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>SSR NOISE</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
-        <is>
-          <t>Author B.</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="9" t="n">
+      <c r="G5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="2">
         <v>2023</v>
       </c>
-      <c r="M5" s="17" t="inlineStr">
-        <is>
-          <t>Near Surface Geophysics</t>
-        </is>
-      </c>
-      <c r="N5" s="17" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="O5" s="16" t="inlineStr">
-        <is>
-          <t>10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="11" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="R5" s="12" t="n">
+      <c r="M5" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="R5" s="5">
         <v>497</v>
       </c>
-      <c r="S5" s="12" t="n"/>
-      <c r="T5" s="12" t="n">
+      <c r="S5" s="5"/>
+      <c r="T5" s="5">
         <v>0.8</v>
       </c>
-      <c r="U5" s="11" t="inlineStr">
-        <is>
-          <t>S-REFL</t>
-        </is>
-      </c>
-      <c r="V5" s="12" t="n"/>
-      <c r="W5" s="12" t="n"/>
-      <c r="X5" s="11" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="Y5" s="9" t="inlineStr">
-        <is>
-          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-        </is>
-      </c>
-      <c r="Z5" s="14" t="inlineStr">
-        <is>
-          <t>Author B.</t>
-        </is>
-      </c>
-      <c r="AA5" s="12" t="n"/>
-      <c r="AB5" s="9" t="n">
+      <c r="U5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="2">
         <v>2023</v>
       </c>
-      <c r="AC5" s="17" t="inlineStr">
-        <is>
-          <t>Near Surface Geophysics</t>
-        </is>
-      </c>
-      <c r="AD5" s="17" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AE5" s="16" t="inlineStr">
-        <is>
-          <t>10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="AF5" s="12" t="n"/>
-      <c r="AG5" s="11" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/nsg.12248</t>
-        </is>
-      </c>
-      <c r="AH5" s="12" t="n"/>
-      <c r="AI5" s="12" t="n"/>
-      <c r="AJ5" s="12" t="n"/>
-      <c r="AK5" s="12" t="n"/>
-      <c r="AL5" s="12" t="n"/>
-      <c r="AM5" s="12" t="n"/>
-      <c r="AN5" s="12" t="n"/>
-      <c r="AO5" s="11" t="n"/>
-      <c r="AP5" s="12" t="n"/>
-      <c r="AQ5" s="12" t="n"/>
-      <c r="AR5" s="12" t="n"/>
-      <c r="AS5" s="12" t="n"/>
-      <c r="AT5" s="12" t="n"/>
+      <c r="AC5" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="5"/>
+      <c r="AO5" s="4"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="5"/>
+      <c r="AS5" s="5"/>
+      <c r="AT5" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddHeader/>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/obspy/io/sitexml/tests/data/sera_site_no_sd.xlsx
+++ b/obspy/io/sitexml/tests/data/sera_site_no_sd.xlsx
@@ -1,400 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiriaki/Desktop/ITSAK/ORFEUS/SITEXML/obspy15/obspy/obspy/io/sitexml/tests/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFC7B17-4B0F-0445-9045-323E8DFD6ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17320" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="siteOwner" sheetId="1" r:id="rId1"/>
-    <sheet name="analysis" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="siteOwner" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="115">
-  <si>
-    <t>ownerID</t>
-  </si>
-  <si>
-    <t>owner_codename</t>
-  </si>
-  <si>
-    <t>owner_fullname</t>
-  </si>
-  <si>
-    <t>personID</t>
-  </si>
-  <si>
-    <t>person_firstname</t>
-  </si>
-  <si>
-    <t>person_lastname</t>
-  </si>
-  <si>
-    <t>person_mbox</t>
-  </si>
-  <si>
-    <t>person_homepage</t>
-  </si>
-  <si>
-    <t>institutionID</t>
-  </si>
-  <si>
-    <t>institution_name</t>
-  </si>
-  <si>
-    <t>institution_mbox</t>
-  </si>
-  <si>
-    <t>institution_phone</t>
-  </si>
-  <si>
-    <t>institution_homepage</t>
-  </si>
-  <si>
-    <t>address_street</t>
-  </si>
-  <si>
-    <t>address_locality</t>
-  </si>
-  <si>
-    <t>address_postal_code</t>
-  </si>
-  <si>
-    <t>address_country_code</t>
-  </si>
-  <si>
-    <t>address_country</t>
-  </si>
-  <si>
-    <t>affiliation_department</t>
-  </si>
-  <si>
-    <t>affiliation_function</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/siteOwner/001</t>
-  </si>
-  <si>
-    <t>SITEOWNER</t>
-  </si>
-  <si>
-    <t>Site Owner Full Name</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/person/001</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Surname</t>
-  </si>
-  <si>
-    <t>someemail@domain.ab</t>
-  </si>
-  <si>
-    <t>https://www.domain.ab/person</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/institution/001</t>
-  </si>
-  <si>
-    <t>INSTITUTION_ABBR</t>
-  </si>
-  <si>
-    <t>info@domain.ab</t>
-  </si>
-  <si>
-    <t>+30 123 456789</t>
-  </si>
-  <si>
-    <t>http://www.domain.ab</t>
-  </si>
-  <si>
-    <t>Some streetAddress</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>Somecountry</t>
-  </si>
-  <si>
-    <t>Seismology</t>
-  </si>
-  <si>
-    <t>Senior researcher</t>
-  </si>
-  <si>
-    <t>siteID</t>
-  </si>
-  <si>
-    <t>siteDescriptionID</t>
-  </si>
-  <si>
-    <t>analysisID</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_value</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_uncertainty</t>
-  </si>
-  <si>
-    <t>resonanceFrequencyQindex1</t>
-  </si>
-  <si>
-    <t>resonanceFrequencyMethod1</t>
-  </si>
-  <si>
-    <t>resonanceFrequencyMethod2</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_title</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_firstAuthor</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_year</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_booktitle</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_language</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_doi</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_description</t>
-  </si>
-  <si>
-    <t>resonanceFrequency_uri</t>
-  </si>
-  <si>
-    <t>velocityS30_value</t>
-  </si>
-  <si>
-    <t>velocityS30_uncertainty</t>
-  </si>
-  <si>
-    <t>velocityS30Qindex1</t>
-  </si>
-  <si>
-    <t>velocityS30Method1</t>
-  </si>
-  <si>
-    <t>velocityS30Method2</t>
-  </si>
-  <si>
-    <t>velocityS30MethodCombIndex</t>
-  </si>
-  <si>
-    <t>velocityS30ManualIndex</t>
-  </si>
-  <si>
-    <t>velocityS30_title</t>
-  </si>
-  <si>
-    <t>velocityS30_firstAuthor</t>
-  </si>
-  <si>
-    <t>velocityS30_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>velocityS30_year</t>
-  </si>
-  <si>
-    <t>velocityS30_booktitle</t>
-  </si>
-  <si>
-    <t>velocityS30_language</t>
-  </si>
-  <si>
-    <t>velocityS30_doi</t>
-  </si>
-  <si>
-    <t>velocityS30_description</t>
-  </si>
-  <si>
-    <t>velocityS30_uri</t>
-  </si>
-  <si>
-    <t>sptLogsCount</t>
-  </si>
-  <si>
-    <t>cptLogsCount</t>
-  </si>
-  <si>
-    <t>boreholeLogsCount</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site_description/001</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/001</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>HVSR NOISE</t>
-  </si>
-  <si>
-    <t>SSR NOISE</t>
-  </si>
-  <si>
-    <t>MASW</t>
-  </si>
-  <si>
-    <t>SPAC/F-K</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
-  </si>
-  <si>
-    <t>Author A.</t>
-  </si>
-  <si>
-    <t>Bulletin Earthquake Engineering</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>10.1007/s10518-017-0135-5</t>
-  </si>
-  <si>
-    <t>paper</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/002</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/003</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site/002</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/site_description/002</t>
-  </si>
-  <si>
-    <t>quakeml:domain.ab/analysis/004</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
-  </si>
-  <si>
-    <t>Author B.</t>
-  </si>
-  <si>
-    <t>Near Surface Geophysics</t>
-  </si>
-  <si>
-    <t>10.1002/nsg.12248</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/nsg.12248</t>
-  </si>
-  <si>
-    <t>S-REFL</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>velocityProfileSetQindex1</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_title</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_firstAuthor</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_secondaryAuthors</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_year</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_booktitle</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_language</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_doi</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_description</t>
-  </si>
-  <si>
-    <t>velocityProfileSet_uri</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <b val="1"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -491,71 +136,71 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -625,14 +270,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1707,776 +1344,1134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="34.1640625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="54.83203125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="29" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" style="10" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" style="10" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" style="10" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="18.33203125" style="10" customWidth="1"/>
-    <col min="17" max="17" width="19.5" style="10" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" style="10" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" style="10" customWidth="1"/>
-    <col min="20" max="20" width="16.1640625" style="10" customWidth="1"/>
-    <col min="21" max="22" width="8.33203125" style="10" customWidth="1"/>
-    <col min="23" max="16384" width="8.33203125" style="10"/>
+    <col width="30.33203125" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
+    <col width="15.6640625" customWidth="1" style="10" min="2" max="2"/>
+    <col width="17.5" bestFit="1" customWidth="1" style="10" min="3" max="3"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="10" min="4" max="4"/>
+    <col width="15.33203125" customWidth="1" style="10" min="5" max="5"/>
+    <col width="15.1640625" customWidth="1" style="10" min="6" max="6"/>
+    <col width="34.1640625" customWidth="1" style="10" min="7" max="7"/>
+    <col width="54.83203125" customWidth="1" style="10" min="8" max="8"/>
+    <col width="29" customWidth="1" style="10" min="9" max="9"/>
+    <col width="17" bestFit="1" customWidth="1" style="10" min="10" max="10"/>
+    <col width="14.6640625" customWidth="1" style="10" min="11" max="11"/>
+    <col width="15.1640625" customWidth="1" style="10" min="12" max="12"/>
+    <col width="18.6640625" customWidth="1" style="10" min="13" max="13"/>
+    <col width="28.6640625" customWidth="1" style="10" min="14" max="14"/>
+    <col width="14.33203125" customWidth="1" style="10" min="15" max="15"/>
+    <col width="18.33203125" customWidth="1" style="10" min="16" max="16"/>
+    <col width="19.5" customWidth="1" style="10" min="17" max="17"/>
+    <col width="14.6640625" customWidth="1" style="10" min="18" max="18"/>
+    <col width="18.83203125" customWidth="1" style="10" min="19" max="19"/>
+    <col width="16.1640625" customWidth="1" style="10" min="20" max="20"/>
+    <col width="8.33203125" customWidth="1" style="10" min="21" max="22"/>
+    <col width="8.33203125" customWidth="1" style="10" min="23" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>19</v>
+    <row r="1" ht="20.25" customHeight="1" s="17">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ownerID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>owner_codename</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>owner_fullname</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>personID</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>person_firstname</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>person_lastname</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>person_mbox</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>person_homepage</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>institutionID</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>institution_name</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>institution_mbox</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>institution_phone</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>institution_homepage</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>address_street</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>address_locality</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>address_postal_code</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>address_country_code</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>address_country</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>affiliation_department</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>affiliation_function</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="15">
+    <row r="2" ht="20.25" customHeight="1" s="17">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/siteOwner/001</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>SITEOWNER</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Site Owner Full Name</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/person/001</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Surname</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>someemail@domain.ab</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>https://www.domain.ab/person</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/institution/001</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>INSTITUTION_ABBR</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>info@domain.ab</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>+30 123 456789</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>http://www.domain.ab</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>Some streetAddress</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="P2" s="15" t="n">
         <v>12345</v>
       </c>
-      <c r="Q2" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>38</v>
+      <c r="Q2" s="12" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="R2" s="12" t="inlineStr">
+        <is>
+          <t>Somecountry</t>
+        </is>
+      </c>
+      <c r="S2" s="12" t="inlineStr">
+        <is>
+          <t>Seismology</t>
+        </is>
+      </c>
+      <c r="T2" s="12" t="inlineStr">
+        <is>
+          <t>Senior researcher</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="isterre.fr/person/001" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M2" r:id="rId2" display="http://www.isterre.fr" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" display="isterre.fr/person/001" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" display="http://www.isterre.fr" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
+    <oddHeader/>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AT5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="49" width="16.33203125" customWidth="1"/>
+    <col width="16.33203125" customWidth="1" style="17" min="1" max="2"/>
+    <col width="20" customWidth="1" style="17" min="3" max="3"/>
+    <col width="16.33203125" customWidth="1" style="17" min="4" max="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>114</v>
+    <row r="1" ht="44.25" customHeight="1" s="17">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>siteID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>siteDescriptionID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>analysisID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_uncertainty</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_qualityIndex</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_method1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_method2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_title</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_firstAuthor</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_year</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_booktitle</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_language</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_doi</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_description</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>resonanceFrequency_uri</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_value</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_uncertainty</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_qualityIndex</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_method1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_method2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_methodCombIndex</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_manualIndex</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_title</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_firstAuthor</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_year</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_booktitle</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_language</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_doi</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_description</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>velocityS30_uri</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>sptLogsCount</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>cptLogsCount</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>boreholeLogsCount</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_qualityIndex</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_title</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_firstAuthor</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_secondaryAuthors</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_year</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_booktitle</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_language</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_doi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_description</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>velocityProfileSet_uri</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="128.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3">
+    <row r="2" ht="128.25" customHeight="1" s="17">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/001</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>HVSR NOISE</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>SSR NOISE</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
+      <c r="R2" s="3" t="n">
         <v>620</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="X2" s="3">
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>MASW</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>SPAC/F-K</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Y2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="2">
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="Z2" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="n"/>
+      <c r="AB2" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="AC2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH2" s="3">
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AD2" s="6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" s="3">
+      <c r="AI2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" s="3">
+      <c r="AJ2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" s="3">
+      <c r="AK2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AL2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM2" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="2">
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="AM2" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AN2" s="3" t="n"/>
+      <c r="AO2" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="AP2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AQ2" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>90</v>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AQ2" s="6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:46" ht="128" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5">
+    <row r="3" ht="128" customHeight="1" s="17">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/001</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/001</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/002</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>HVSR NOISE</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>SSR NOISE</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="n">
         <v>620</v>
       </c>
-      <c r="S3" s="5">
+      <c r="S3" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="T3" s="5">
+      <c r="T3" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="X3" s="5">
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>MASW</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>SPAC/F-K</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="2">
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="Z3" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="n"/>
+      <c r="AB3" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="AC3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF3" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG3" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH3" s="5">
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AD3" s="7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="AH3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" s="5">
+      <c r="AI3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" s="5">
+      <c r="AJ3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AK3" s="5">
+      <c r="AK3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="AL3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN3" s="5"/>
-      <c r="AO3" s="4">
+      <c r="AL3" s="4" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="AM3" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AN3" s="5" t="n"/>
+      <c r="AO3" s="4" t="n">
         <v>2018</v>
       </c>
-      <c r="AP3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AQ3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AS3" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AT3" s="4" t="s">
-        <v>90</v>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AQ3" s="7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AS3" s="4" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="128" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5">
+    <row r="4" ht="128" customHeight="1" s="17">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/001</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/001</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/003</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>HVSR NOISE</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>SSR NOISE</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n">
         <v>620</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="T4" s="5">
+      <c r="T4" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="U4" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="X4" s="5">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>MASW</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>SPAC/F-K</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="2">
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="Z4" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="AC4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD4" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH4" s="5">
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AD4" s="7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AG4" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
+      </c>
+      <c r="AH4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" s="5">
+      <c r="AI4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" s="5">
+      <c r="AJ4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AK4" s="5">
+      <c r="AK4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="AL4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM4" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN4" s="5"/>
-      <c r="AO4" s="4">
+      <c r="AL4" s="4" t="inlineStr">
+        <is>
+          <t>Characterization of site conditions (soil class, Vs30, velocity profiles) for 33 stations from the French permanent accelerometric network (RAP) using surface-wave methods</t>
+        </is>
+      </c>
+      <c r="AM4" s="6" t="inlineStr">
+        <is>
+          <t>Author A.</t>
+        </is>
+      </c>
+      <c r="AN4" s="5" t="n"/>
+      <c r="AO4" s="4" t="n">
         <v>2018</v>
       </c>
-      <c r="AP4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AQ4" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AS4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AT4" s="4" t="s">
-        <v>90</v>
+      <c r="AP4" s="4" t="inlineStr">
+        <is>
+          <t>Bulletin Earthquake Engineering</t>
+        </is>
+      </c>
+      <c r="AQ4" s="7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>10.1007/s10518-017-0135-5</t>
+        </is>
+      </c>
+      <c r="AS4" s="4" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="AT4" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10518-017-0135-5/</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="44" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5">
+    <row r="5" ht="44" customHeight="1" s="17">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site/002</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/site_description/002</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>quakeml:domain.ab/analysis/004</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="2">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>SSR NOISE</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="M5" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="R5" s="5">
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="n">
         <v>497</v>
       </c>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5">
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="U5" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="2">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>S-REFL</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>Combination of passive and active methods towards site characterization of accelerometer stations in Greece</t>
+        </is>
+      </c>
+      <c r="Z5" s="6" t="inlineStr">
+        <is>
+          <t>Author B.</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="AC5" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD5" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AF5" s="5"/>
-      <c r="AG5" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5"/>
-      <c r="AJ5" s="5"/>
-      <c r="AK5" s="5"/>
-      <c r="AL5" s="5"/>
-      <c r="AM5" s="5"/>
-      <c r="AN5" s="5"/>
-      <c r="AO5" s="4"/>
-      <c r="AP5" s="5"/>
-      <c r="AQ5" s="5"/>
-      <c r="AR5" s="5"/>
-      <c r="AS5" s="5"/>
-      <c r="AT5" s="5"/>
+      <c r="AC5" s="8" t="inlineStr">
+        <is>
+          <t>Near Surface Geophysics</t>
+        </is>
+      </c>
+      <c r="AD5" s="8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AE5" s="7" t="inlineStr">
+        <is>
+          <t>10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/nsg.12248</t>
+        </is>
+      </c>
+      <c r="AH5" s="5" t="n"/>
+      <c r="AI5" s="5" t="n"/>
+      <c r="AJ5" s="5" t="n"/>
+      <c r="AK5" s="5" t="n"/>
+      <c r="AL5" s="5" t="n"/>
+      <c r="AM5" s="5" t="n"/>
+      <c r="AN5" s="5" t="n"/>
+      <c r="AO5" s="4" t="n"/>
+      <c r="AP5" s="5" t="n"/>
+      <c r="AQ5" s="5" t="n"/>
+      <c r="AR5" s="5" t="n"/>
+      <c r="AS5" s="5" t="n"/>
+      <c r="AT5" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
+    <oddHeader/>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>